--- a/Mediciones/Exploracion/Serpiente/RUN_4_5M_Serp_6NO.xlsx
+++ b/Mediciones/Exploracion/Serpiente/RUN_4_5M_Serp_6NO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Henry\Desktop\Exploracion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GiHub\Resultados_Doc\Mediciones\Exploracion\Serpiente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4154C4-A990-4685-9F19-9C74C2E890D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B807955-992A-4370-8AC8-CF9190FE632B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>2026-07-17T15:58:39</t>
-  </si>
-  <si>
-    <t>Centro de gravedad</t>
   </si>
   <si>
     <t>2026-07-17T15:58:41</t>
@@ -418,6 +415,9 @@
   "run_id": "R20260717_155839",
   "repetition": 1
 }</t>
+  </si>
+  <si>
+    <t>Exploracion frontera</t>
   </si>
 </sst>
 </file>
@@ -773,7 +773,7 @@
     </row>
     <row r="2" spans="1:1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -853,7 +853,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D2">
         <v>1.3530196681417981E-2</v>
@@ -888,13 +888,13 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D3">
         <v>1.7369279358483428E-2</v>
@@ -929,13 +929,13 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D4">
         <v>1.7369279358483428E-2</v>
@@ -970,13 +970,13 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D5">
         <v>1.743324564324706E-2</v>
@@ -1011,13 +1011,13 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D6">
         <v>1.743324564324706E-2</v>
@@ -1052,13 +1052,13 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D7">
         <v>1.743324564324706E-2</v>
@@ -1093,13 +1093,13 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D8">
         <v>1.743324564324706E-2</v>
@@ -1134,13 +1134,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D9">
         <v>1.743324564324706E-2</v>
@@ -1175,13 +1175,13 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D10">
         <v>1.743324564324706E-2</v>
@@ -1216,13 +1216,13 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D11">
         <v>1.743324564324706E-2</v>
@@ -1257,13 +1257,13 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D12">
         <v>1.743324564324706E-2</v>
@@ -1298,13 +1298,13 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D13">
         <v>1.743324564324706E-2</v>
@@ -1339,13 +1339,13 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D14">
         <v>1.743324564324706E-2</v>
@@ -1380,13 +1380,13 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D15">
         <v>1.743324564324706E-2</v>
@@ -1421,13 +1421,13 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D16">
         <v>1.743324564324706E-2</v>
@@ -1462,13 +1462,13 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D17">
         <v>1.743324564324706E-2</v>
@@ -1503,13 +1503,13 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18">
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D18">
         <v>1.743324564324706E-2</v>
@@ -1544,13 +1544,13 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19">
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D19">
         <v>1.743324564324706E-2</v>
@@ -1585,13 +1585,13 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D20">
         <v>1.743324564324706E-2</v>
@@ -1626,13 +1626,13 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D21">
         <v>1.743324564324706E-2</v>
@@ -1667,13 +1667,13 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22">
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D22">
         <v>1.743324564324706E-2</v>
@@ -1708,13 +1708,13 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B23">
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D23">
         <v>1.8245995582208539E-2</v>
@@ -1749,13 +1749,13 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24">
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D24">
         <v>1.8245995582208539E-2</v>
@@ -1790,13 +1790,13 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25">
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D25">
         <v>1.8573183989018281E-2</v>
@@ -1831,13 +1831,13 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26">
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D26">
         <v>1.8573183989018281E-2</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27">
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D27">
         <v>1.8573183989018281E-2</v>
@@ -1913,13 +1913,13 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28">
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D28">
         <v>1.8573183989018281E-2</v>
@@ -1954,13 +1954,13 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29">
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D29">
         <v>1.8573183989018281E-2</v>
@@ -1995,13 +1995,13 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30">
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D30">
         <v>1.8573183989018281E-2</v>
@@ -2036,13 +2036,13 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B31">
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D31">
         <v>1.8573183989018281E-2</v>
@@ -2077,13 +2077,13 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B32">
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D32">
         <v>1.8573183989018281E-2</v>
@@ -2118,13 +2118,13 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B33">
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D33">
         <v>1.8573183989018281E-2</v>
@@ -2159,13 +2159,13 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34">
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D34">
         <v>2.0738702231076791E-2</v>
@@ -2200,13 +2200,13 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B35">
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D35">
         <v>2.1152773872421909E-2</v>
@@ -2241,13 +2241,13 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B36">
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D36">
         <v>2.1152773872421909E-2</v>
@@ -2282,13 +2282,13 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B37">
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D37">
         <v>2.1152773872421909E-2</v>
@@ -2323,13 +2323,13 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B38">
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D38">
         <v>2.1152773872421909E-2</v>
@@ -2364,13 +2364,13 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B39">
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D39">
         <v>2.1152773872421909E-2</v>
@@ -2405,13 +2405,13 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B40">
         <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D40">
         <v>2.5791896573803898E-2</v>
@@ -2446,13 +2446,13 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B41">
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D41">
         <v>2.5791896573803898E-2</v>
@@ -2487,13 +2487,13 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B42">
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D42">
         <v>3.0053010967929839E-2</v>
@@ -2528,13 +2528,13 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B43">
         <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D43">
         <v>0.19694654377110901</v>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B44">
         <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D44">
         <v>0.63026594342553288</v>
@@ -2610,13 +2610,13 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B45">
         <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D45">
         <v>0.83002155832617652</v>
@@ -2651,13 +2651,13 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B46">
         <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D46">
         <v>0.83002155832617652</v>
@@ -2692,13 +2692,13 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47">
         <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D47">
         <v>0.98863535101412636</v>
@@ -2733,13 +2733,13 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B48">
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D48">
         <v>0.98863535101412636</v>
@@ -2774,13 +2774,13 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B49">
         <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D49">
         <v>0.98863535101412636</v>
@@ -2815,13 +2815,13 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B50">
         <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D50">
         <v>0.98863535101412636</v>
@@ -2856,13 +2856,13 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B51">
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D51">
         <v>0.98863535101412636</v>
@@ -2897,13 +2897,13 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52">
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D52">
         <v>0.98863535101412636</v>
@@ -2938,13 +2938,13 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53">
         <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D53">
         <v>0.98863535101412636</v>
@@ -2979,13 +2979,13 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54">
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D54">
         <v>0.98863535101412636</v>
@@ -3020,13 +3020,13 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B55">
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D55">
         <v>0.98863535101412636</v>
@@ -3061,13 +3061,13 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B56">
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D56">
         <v>0.98863535101412636</v>
@@ -3102,13 +3102,13 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B57">
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D57">
         <v>0.98863535101412636</v>
@@ -3143,13 +3143,13 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B58">
         <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D58">
         <v>0.98863535101412636</v>
@@ -3184,13 +3184,13 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B59">
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D59">
         <v>0.98863535101412636</v>
@@ -3225,13 +3225,13 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B60">
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D60">
         <v>0.98863535101412636</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B61">
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D61">
         <v>0.98863535101412636</v>
@@ -3307,13 +3307,13 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B62">
         <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D62">
         <v>0.98863535101412636</v>
@@ -3348,13 +3348,13 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B63">
         <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D63">
         <v>0.98863535101412636</v>
@@ -3389,13 +3389,13 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B64">
         <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D64">
         <v>0.98863535101412636</v>
@@ -3430,13 +3430,13 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B65">
         <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D65">
         <v>0.98863535101412636</v>
@@ -3471,13 +3471,13 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B66">
         <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D66">
         <v>0.98863535101412636</v>
@@ -3512,13 +3512,13 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B67">
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D67">
         <v>0.98863535101412636</v>
@@ -3553,13 +3553,13 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B68">
         <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D68">
         <v>0.98863535101412636</v>
@@ -3594,13 +3594,13 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B69">
         <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D69">
         <v>0.98863535101412636</v>
@@ -3635,13 +3635,13 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B70">
         <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D70">
         <v>0.98863535101412636</v>
@@ -3676,13 +3676,13 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B71">
         <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D71">
         <v>0.98863535101412636</v>
@@ -3717,13 +3717,13 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B72">
         <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D72">
         <v>0.98863535101412636</v>
@@ -3758,13 +3758,13 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B73">
         <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D73">
         <v>0.98863535101412636</v>
@@ -3799,13 +3799,13 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B74">
         <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D74">
         <v>0.98863535101412636</v>
@@ -3840,13 +3840,13 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B75">
         <v>73</v>
       </c>
       <c r="C75" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D75">
         <v>0.98863535101412636</v>
@@ -3881,13 +3881,13 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B76">
         <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D76">
         <v>0.98863535101412636</v>
@@ -3922,13 +3922,13 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B77">
         <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D77">
         <v>0.98863535101412636</v>
@@ -3963,13 +3963,13 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B78">
         <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D78">
         <v>0.98863535101412636</v>
@@ -4004,13 +4004,13 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B79">
         <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D79">
         <v>0.98863535101412636</v>
@@ -4045,13 +4045,13 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B80">
         <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D80">
         <v>0.98863535101412636</v>
@@ -4086,13 +4086,13 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B81">
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D81">
         <v>0.98863535101412636</v>
@@ -4127,13 +4127,13 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B82">
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D82">
         <v>0.98863535101412636</v>
@@ -4168,13 +4168,13 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B83">
         <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D83">
         <v>0.98863535101412636</v>
@@ -4209,13 +4209,13 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B84">
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D84">
         <v>0.98863535101412636</v>
@@ -4250,13 +4250,13 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B85">
         <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D85">
         <v>0.98863535101412636</v>
@@ -4291,13 +4291,13 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B86">
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D86">
         <v>0.98863535101412636</v>
@@ -4332,13 +4332,13 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B87">
         <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D87">
         <v>0.98863535101412636</v>
@@ -4373,13 +4373,13 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B88">
         <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D88">
         <v>0.98863535101412636</v>
@@ -4414,13 +4414,13 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B89">
         <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D89">
         <v>0.98863535101412636</v>
@@ -4455,13 +4455,13 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B90">
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D90">
         <v>0.98863535101412636</v>
@@ -4496,13 +4496,13 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B91">
         <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D91">
         <v>0.98863535101412636</v>
@@ -4537,13 +4537,13 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B92">
         <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D92">
         <v>0.98863535101412636</v>
@@ -4578,13 +4578,13 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B93">
         <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D93">
         <v>0.98863535101412636</v>
@@ -4619,13 +4619,13 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B94">
         <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D94">
         <v>0.98863535101412636</v>
@@ -4660,13 +4660,13 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B95">
         <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D95">
         <v>0.98863535101412636</v>
@@ -4701,13 +4701,13 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B96">
         <v>94</v>
       </c>
       <c r="C96" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D96">
         <v>0.98863535101412636</v>
@@ -4742,13 +4742,13 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B97">
         <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D97">
         <v>0.98863535101412636</v>
@@ -4783,13 +4783,13 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B98">
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D98">
         <v>0.98863535101412636</v>
@@ -4824,13 +4824,13 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B99">
         <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D99">
         <v>0.98863535101412636</v>
@@ -4865,13 +4865,13 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B100">
         <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D100">
         <v>0.98863535101412636</v>
@@ -4906,13 +4906,13 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B101">
         <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D101">
         <v>0.98863535101412636</v>
@@ -4947,13 +4947,13 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B102">
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D102">
         <v>0.98863535101412636</v>
@@ -4988,13 +4988,13 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B103">
         <v>101</v>
       </c>
       <c r="C103" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D103">
         <v>0.98863535101412636</v>
@@ -5029,13 +5029,13 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B104">
         <v>102</v>
       </c>
       <c r="C104" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D104">
         <v>0.98863535101412636</v>
@@ -5070,13 +5070,13 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B105">
         <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D105">
         <v>0.98863535101412636</v>
@@ -5111,13 +5111,13 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B106">
         <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D106">
         <v>0.98863535101412636</v>
@@ -5152,13 +5152,13 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B107">
         <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D107">
         <v>0.98863535101412636</v>
@@ -5193,13 +5193,13 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B108">
         <v>106</v>
       </c>
       <c r="C108" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D108">
         <v>0.98863535101412636</v>
@@ -5234,13 +5234,13 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B109">
         <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D109">
         <v>0.98863535101412636</v>
@@ -5275,13 +5275,13 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B110">
         <v>108</v>
       </c>
       <c r="C110" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D110">
         <v>0.98863535101412636</v>
@@ -5316,13 +5316,13 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B111">
         <v>109</v>
       </c>
       <c r="C111" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D111">
         <v>0.98863535101412636</v>
@@ -5357,13 +5357,13 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B112">
         <v>110</v>
       </c>
       <c r="C112" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D112">
         <v>0.98863535101412636</v>
@@ -5398,13 +5398,13 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B113">
         <v>111</v>
       </c>
       <c r="C113" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D113">
         <v>0.98863535101412636</v>
@@ -5439,13 +5439,13 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B114">
         <v>112</v>
       </c>
       <c r="C114" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D114">
         <v>0.98863535101412636</v>
@@ -5480,13 +5480,13 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B115">
         <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D115">
         <v>0.98863535101412636</v>
@@ -5521,13 +5521,13 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B116">
         <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D116">
         <v>0.98863535101412636</v>
@@ -5562,13 +5562,13 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B117">
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D117">
         <v>0.98863535101412636</v>
@@ -5603,13 +5603,13 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B118">
         <v>116</v>
       </c>
       <c r="C118" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D118">
         <v>0.98863535101412636</v>
@@ -5644,13 +5644,13 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B119">
         <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D119">
         <v>0.98863535101412636</v>
@@ -5685,13 +5685,13 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B120">
         <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D120">
         <v>0.98863535101412636</v>
@@ -5726,13 +5726,13 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B121">
         <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D121">
         <v>0.98863535101412636</v>
@@ -5782,25 +5782,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" t="s">
         <v>67</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>68</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>69</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>70</v>
-      </c>
-      <c r="G1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -7107,10 +7107,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" t="s">
         <v>72</v>
-      </c>
-      <c r="B1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -7170,13 +7170,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -7801,16 +7801,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" t="s">
         <v>75</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>76</v>
-      </c>
-      <c r="D1" t="s">
-        <v>77</v>
       </c>
       <c r="E1" t="s">
         <v>10</v>
@@ -9668,16 +9668,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" t="s">
         <v>78</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>79</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>80</v>
-      </c>
-      <c r="D1" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -9696,15 +9696,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" t="s">
         <v>82</v>
-      </c>
-      <c r="B1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -9712,7 +9712,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B3">
         <v>1.9</v>
@@ -9720,7 +9720,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9728,7 +9728,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B5">
         <v>1.2</v>
@@ -9739,12 +9739,12 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B7">
         <v>120</v>
@@ -9776,7 +9776,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B11">
         <v>0.98863500000000004</v>
@@ -9784,7 +9784,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B12">
         <v>1.3741613400052299</v>
@@ -9792,7 +9792,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13">
         <v>80.77065589997801</v>
@@ -9800,7 +9800,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B14">
         <v>1.701312592665976E-2</v>
@@ -9808,7 +9808,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -9816,12 +9816,12 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B17">
         <v>0</v>
